--- a/make_test_file/قوالب/قالب - استمارة تعاهد للدورات .xlsx
+++ b/make_test_file/قوالب/قالب - استمارة تعاهد للدورات .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODE\scripts\make_test_file\قوالب\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E09D4C-02A3-416A-B943-E2F64AB93281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC3EEA0-8772-4710-94E9-E2DD163E8C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
     <t>التقدير</t>
   </si>
   <si>
-    <t>إدارة الاختبارات 1446 هـ</t>
+    <t>إدارة الاختبارات 1447 هـ</t>
   </si>
 </sst>
 </file>
@@ -760,34 +760,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -827,6 +799,34 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1083,21 +1083,21 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="23" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="22"/>
+      <c r="I2" s="55"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1145,13 +1145,13 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="26"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="51"/>
       <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1181,13 +1181,13 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="26"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
@@ -1243,19 +1243,19 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="47"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="33"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1275,15 +1275,15 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="44"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="50"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="36"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1303,47 +1303,47 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="51"/>
-      <c r="B9" s="54" t="s">
+      <c r="A9" s="37"/>
+      <c r="B9" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="35" t="s">
+      <c r="L9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M9" s="35" t="s">
+      <c r="M9" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="N9" s="35" t="s">
+      <c r="N9" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="35" t="s">
+      <c r="O9" s="21" t="s">
         <v>16</v>
       </c>
       <c r="P9" s="2"/>
@@ -1359,21 +1359,21 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="52"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -1387,7 +1387,7 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="52"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="6">
         <v>1</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="52"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="6">
         <v>2</v>
       </c>
@@ -1489,7 +1489,7 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="52"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="6">
         <v>3</v>
       </c>
@@ -1540,7 +1540,7 @@
       <c r="Z13" s="2"/>
     </row>
     <row r="14" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="52"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="6">
         <v>4</v>
       </c>
@@ -1591,7 +1591,7 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="52"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="6">
         <v>5</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="Z15" s="2"/>
     </row>
     <row r="16" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="52"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="6">
         <v>6</v>
       </c>
@@ -1693,7 +1693,7 @@
       <c r="Z16" s="2"/>
     </row>
     <row r="17" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="52"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="6">
         <v>7</v>
       </c>
@@ -1744,7 +1744,7 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="52"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="6">
         <v>8</v>
       </c>
@@ -1795,7 +1795,7 @@
       <c r="Z18" s="2"/>
     </row>
     <row r="19" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="52"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="13">
         <v>9</v>
       </c>
@@ -1846,7 +1846,7 @@
       <c r="Z19" s="2"/>
     </row>
     <row r="20" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="52"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="13">
         <v>10</v>
       </c>
@@ -1897,16 +1897,16 @@
       <c r="Z20" s="2"/>
     </row>
     <row r="21" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="52"/>
-      <c r="B21" s="37" t="s">
+      <c r="A21" s="38"/>
+      <c r="B21" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="25"/>
       <c r="I21" s="17" t="str">
         <f>IF(AND(I11 = "", I12 = "", I13 = "", I14 = "", I15 = "", I16 = "", I17 = "", I18 = "", I19 = "",I20 = ""), "", (SUM(I11:I20) / (COUNT(I11:I20) * 10)) * 100)</f>
         <v/>
@@ -1930,16 +1930,16 @@
       <c r="Z21" s="2"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="53"/>
-      <c r="B22" s="40" t="s">
+      <c r="A22" s="39"/>
+      <c r="B22" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="42"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="28"/>
       <c r="I22" s="19" t="str">
         <f>IF(I21 = "", "", IF(I21 &gt;= 90, "ممتاز", IF(I21 &gt;= 80, "جيدجدا", IF(I21 &gt;= 70, "جيد", "راسب"))))</f>
         <v/>
@@ -29348,6 +29348,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
     <mergeCell ref="N9:N10"/>
     <mergeCell ref="O9:O10"/>
     <mergeCell ref="B21:H21"/>
@@ -29364,16 +29374,6 @@
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="M9:M10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
   </mergeCells>
   <conditionalFormatting sqref="I21">
     <cfRule type="colorScale" priority="1">
